--- a/Files/WebElemets.xlsx
+++ b/Files/WebElemets.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>Key</t>
   </si>
@@ -50,7 +50,7 @@
     <t>ClickloginButton</t>
   </si>
   <si>
-    <t>//button[text()=' Login ']</t>
+    <t>//button[@type='submit']</t>
   </si>
   <si>
     <t>ClickPIM</t>
@@ -92,73 +92,97 @@
     <t>empSaveButton</t>
   </si>
   <si>
+    <t>//h6[text()='Add Employee']/parent::div/descendant::button[@type='submit']</t>
+  </si>
+  <si>
+    <t>validateEmployeeCreation</t>
+  </si>
+  <si>
+    <t>//h6[text()="#replace"]</t>
+  </si>
+  <si>
+    <t>ClickUserIcon</t>
+  </si>
+  <si>
+    <t>//i[contains(@class,'userdropdown-icon')]</t>
+  </si>
+  <si>
+    <t>ClickLogout</t>
+  </si>
+  <si>
+    <t>//a[text()="Logout"]</t>
+  </si>
+  <si>
+    <t>ClickRecruitment</t>
+  </si>
+  <si>
+    <t>//span[text()="Recruitment"]</t>
+  </si>
+  <si>
+    <t>ClickVacancies</t>
+  </si>
+  <si>
+    <t>//a[text()="Vacancies"]</t>
+  </si>
+  <si>
+    <t>ClickAddVacancy</t>
+  </si>
+  <si>
+    <t>//i[@class="oxd-icon bi-plus oxd-button-icon"]</t>
+  </si>
+  <si>
+    <t>vacancyName</t>
+  </si>
+  <si>
+    <t>//label[text()='Vacancy Name']/ancestor::div[contains(@class,'wrapper')]/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>ClickJobTitleDropdown</t>
+  </si>
+  <si>
+    <t>//label[text()="Job Title"]/parent::div/following-sibling::div//div[contains(text(),'Select')]</t>
+  </si>
+  <si>
+    <t>ClickJobTitleOption</t>
+  </si>
+  <si>
+    <t>//div[@role='listbox']/div/span[text()="#replace"]</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>//label[text()='Description']/ancestor::div[contains(@class,'wrapper')]/following-sibling::div/textarea</t>
+  </si>
+  <si>
+    <t>hiringManager</t>
+  </si>
+  <si>
+    <t>//label[text()='Hiring Manager']/ancestor::div/descendant::input[contains(@placeholder,"Type")]</t>
+  </si>
+  <si>
+    <t>ClickHiringManagerSuggestion</t>
+  </si>
+  <si>
+    <t>//div[@role="listbox"]/div/span[text()="#replace"]</t>
+  </si>
+  <si>
+    <t>noOfPositions</t>
+  </si>
+  <si>
+    <t>//label[text()='Number of Positions']/ancestor::div/following-sibling::div/input</t>
+  </si>
+  <si>
+    <t>saveVacancyButton</t>
+  </si>
+  <si>
     <t>//button[@type="submit"]</t>
   </si>
   <si>
-    <t>validateEmployeeCreation</t>
-  </si>
-  <si>
-    <t>//h6[text()="#replace"]</t>
-  </si>
-  <si>
-    <t>ClickUserIcon</t>
-  </si>
-  <si>
-    <t>//i[contains(@class,'userdropdown-icon')]</t>
-  </si>
-  <si>
-    <t>ClickLogout</t>
-  </si>
-  <si>
-    <t>//a[text()="Logout"]</t>
-  </si>
-  <si>
-    <t>ClickRecruitment</t>
-  </si>
-  <si>
-    <t>//span[text()="Recruitment"]</t>
-  </si>
-  <si>
-    <t>ClickVacancies</t>
-  </si>
-  <si>
-    <t>//a[text()="Vacancies"]</t>
-  </si>
-  <si>
-    <t>ClickAddVacancy</t>
-  </si>
-  <si>
-    <t>//i[@class="oxd-icon bi-plus oxd-button-icon"]</t>
-  </si>
-  <si>
-    <t>vacancyName</t>
-  </si>
-  <si>
-    <t>//label[text()='Vacancy Name']/ancestor::div[contains(@class,'wrapper')]/following-sibling::div/input</t>
-  </si>
-  <si>
-    <t>jobTitle</t>
-  </si>
-  <si>
-    <t>//span[text()="Automaton Tester"]</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>//label[text()='Description']/ancestor::div[contains(@class,'wrapper')]/following-sibling::div/textarea</t>
-  </si>
-  <si>
-    <t>hiringManager</t>
-  </si>
-  <si>
-    <t>//label[text()='Hiring Manager']/ancestor::div/descendant::input[contains(@placeholder,"Type")]</t>
-  </si>
-  <si>
-    <t>noOfPositions</t>
-  </si>
-  <si>
-    <t>//label[text()='Number of Positions']/ancestor::div/following-sibling::div/input</t>
+    <t>validateVacancyCreation</t>
+  </si>
+  <si>
+    <t>//h6[text()="Edit Vacancy"]</t>
   </si>
   <si>
     <t>ClickAddCandidate</t>
@@ -206,10 +230,7 @@
     <t>contactNo</t>
   </si>
   <si>
-    <t>//label[text()='Contact Number']/ancestor::div[contains(@class,'wrapper')]/following-sibling::div/input[@placeholder='Type here']</t>
-  </si>
-  <si>
-    <t>resume</t>
+    <t>//label[text()='Contact Number']/parent::div/following-sibling::div/input</t>
   </si>
   <si>
     <t>notes</t>
@@ -219,6 +240,12 @@
   </si>
   <si>
     <t>ClickCandidateSaveButton</t>
+  </si>
+  <si>
+    <t>validateCandidateStatus</t>
+  </si>
+  <si>
+    <t>//p[text()="Status: Application Initiated"]</t>
   </si>
 </sst>
 </file>
@@ -1178,11 +1205,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
-    <col min="2" max="2" width="109.555555555556" customWidth="1"/>
+    <col min="2" max="2" width="119.666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1333,122 +1360,152 @@
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="3" t="s">
-        <v>44</v>
+      <c r="A24" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2" t="s">
-        <v>46</v>
+      <c r="A25" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2" t="s">
-        <v>48</v>
+      <c r="A26" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2" t="s">
-        <v>50</v>
+      <c r="A27" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>21</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
